--- a/astro-site/public/dl/coffee-shop-checklist-templates/08-cafe-opening-closing-checklist.xlsx
+++ b/astro-site/public/dl/coffee-shop-checklist-templates/08-cafe-opening-closing-checklist.xlsx
@@ -977,7 +977,7 @@
       </c>
       <c r="E5" s="19" t="inlineStr">
         <is>
-          <t>6:45 AM</t>
+          <t>6:30 AM</t>
         </is>
       </c>
       <c r="F5" s="19" t="inlineStr"/>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="E6" s="19" t="inlineStr">
         <is>
-          <t>6:45 AM</t>
+          <t>6:30 AM</t>
         </is>
       </c>
       <c r="F6" s="19" t="inlineStr"/>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="E7" s="19" t="inlineStr">
         <is>
-          <t>6:45 AM</t>
+          <t>6:30 AM</t>
         </is>
       </c>
       <c r="F7" s="19" t="inlineStr"/>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="E8" s="19" t="inlineStr">
         <is>
-          <t>6:45 AM</t>
+          <t>6:30 AM</t>
         </is>
       </c>
       <c r="F8" s="19" t="inlineStr"/>
@@ -1135,7 +1135,7 @@
       </c>
       <c r="C11" s="19" t="inlineStr">
         <is>
-          <t>Host stand</t>
+          <t>Front counter</t>
         </is>
       </c>
       <c r="D11" s="19" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="C13" s="19" t="inlineStr">
         <is>
-          <t>Host stand</t>
+          <t>Front counter</t>
         </is>
       </c>
       <c r="D13" s="19" t="inlineStr">
